--- a/outputs/daily/hr_rankings_2026-06-25.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-25.xlsx
@@ -1955,7 +1955,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 2</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
@@ -19911,7 +19911,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
@@ -23007,7 +23007,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 6</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
@@ -25496,11 +25496,19 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
@@ -25515,7 +25523,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
@@ -29131,7 +29139,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29151,7 +29159,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
@@ -35033,7 +35041,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -35053,7 +35061,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 3</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-06-25.xlsx
+++ b/outputs/daily/hr_rankings_2026-06-25.xlsx
@@ -1950,34 +1950,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2168,7 +2164,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3564,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4692,7 +4688,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4972,7 +4968,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7212,7 +7208,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8670,34 +8666,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8954,34 +8946,30 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10292,7 +10280,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -12322,34 +12310,30 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13380,7 +13364,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13660,7 +13644,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14508,7 +14492,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -14788,7 +14772,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -19322,34 +19306,30 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -19886,34 +19866,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -20956,7 +20932,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -22360,7 +22336,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -22982,34 +22958,30 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23200,7 +23172,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -24316,7 +24288,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -25498,34 +25470,30 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26272,7 +26240,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -28504,7 +28472,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -29134,34 +29102,30 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32684,7 +32648,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -32964,7 +32928,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -35036,34 +35000,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -35254,7 +35214,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -36650,7 +36610,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -37778,7 +37738,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -38058,7 +38018,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
